--- a/r5-ELGA-MOPED-339-Operation--erweitern-um-Hauptversichertenlogik/StructureDefinition-moped-ext-anzahlVerlegungen.xlsx
+++ b/r5-ELGA-MOPED-339-Operation--erweitern-um-Hauptversichertenlogik/StructureDefinition-moped-ext-anzahlVerlegungen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:43:28+00:00</t>
+    <t>2025-02-07T07:29:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
